--- a/artifacts/tables.xlsx
+++ b/artifacts/tables.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="개요" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="jobs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="job_history" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="task_history" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="executor_status" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="executor_reservation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="coordinator_status" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="executor_health_metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jobs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="job_history" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="task_history" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="executor_status" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="executor_reservation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coordinator_status" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="executor_health_metrics" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -672,6 +672,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -863,6 +864,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1191,6 +1193,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -1208,8 +1211,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1255,6 +1258,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2047,6 +2051,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3095,6 +3100,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3707,6 +3713,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3995,6 +4002,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4104,7 +4112,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>생존 신호 시각</t>
+          <t>heartbeat 시각</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -4187,6 +4195,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4679,6 +4688,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
